--- a/tools/importer/reports/import-homepage.report.xlsx
+++ b/tools/importer/reports/import-homepage.report.xlsx
@@ -52,7 +52,7 @@
     <t>homepage</t>
   </si>
   <si>
-    <t>2026-08-19T04:57:17.732Z</t>
+    <t>2026-09-28T19:18:39.187Z</t>
   </si>
   <si>
     <t>Comprehensive Shipping Insurance for SMBs | InsureShield</t>

--- a/tools/importer/reports/import-homepage.report.xlsx
+++ b/tools/importer/reports/import-homepage.report.xlsx
@@ -52,7 +52,7 @@
     <t>homepage</t>
   </si>
   <si>
-    <t>2026-09-28T19:18:39.187Z</t>
+    <t>2026-09-28T20:11:55.664Z</t>
   </si>
   <si>
     <t>Comprehensive Shipping Insurance for SMBs | InsureShield</t>
